--- a/output/Results_3D_Master_Synthesis.xlsx
+++ b/output/Results_3D_Master_Synthesis.xlsx
@@ -590,7 +590,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Confirmed by brms and My Model (Rescued Intermediate)</t>
+          <t>Confirmed by brms and GP-GLMM (Rescued Intermediate)</t>
         </is>
       </c>
     </row>
